--- a/sources/table_normalization/xlsx/education-table17.xlsx
+++ b/sources/table_normalization/xlsx/education-table17.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
   <si>
     <t>State</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>Two or more races</t>
-  </si>
-  <si>
-    <t>`</t>
   </si>
   <si>
     <t>Number</t>
@@ -797,10 +794,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -858,15 +851,6 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -881,6 +865,19 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1379,158 +1376,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" ht="25" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="57" t="s">
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="58"/>
-      <c r="S1" s="57" t="s">
+      <c r="R1" s="56"/>
+      <c r="S1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="58"/>
-      <c r="U1" s="57" t="s">
+      <c r="T1" s="56"/>
+      <c r="U1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="V1" s="58"/>
-      <c r="W1" s="53" t="s">
+      <c r="V1" s="56"/>
+      <c r="W1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="X1" s="55" t="s">
+      <c r="X1" s="53" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:24" s="1" customFormat="1" ht="32" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="64" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="65"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="60"/>
+      <c r="G2" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="60"/>
+      <c r="I2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="65"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="60"/>
+      <c r="K2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="65"/>
-      <c r="M2" s="67" t="s">
+      <c r="L2" s="60"/>
+      <c r="M2" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="65"/>
-      <c r="O2" s="67" t="s">
+      <c r="N2" s="60"/>
+      <c r="O2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="56"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="54"/>
     </row>
     <row r="3" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="D3" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="E3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="43" t="s">
+      <c r="S3" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="T3" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="43" t="s">
+      <c r="U3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="V3" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="P3" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="S3" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="U3" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="V3" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="W3" s="47"/>
-      <c r="X3" s="48"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="46"/>
     </row>
     <row r="4" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="8">
         <v>6731214</v>
@@ -1604,7 +1599,7 @@
     </row>
     <row r="5" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="13">
         <v>91696</v>
@@ -1678,7 +1673,7 @@
     </row>
     <row r="6" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="8">
         <v>29376</v>
@@ -1752,7 +1747,7 @@
     </row>
     <row r="7" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="13">
         <v>178878</v>
@@ -1826,7 +1821,7 @@
     </row>
     <row r="8" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="8">
         <v>54783</v>
@@ -1900,7 +1895,7 @@
     </row>
     <row r="9" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="13">
         <v>729338</v>
@@ -1974,7 +1969,7 @@
     </row>
     <row r="10" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="8">
         <v>139970</v>
@@ -2048,7 +2043,7 @@
     </row>
     <row r="11" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="13">
         <v>77731</v>
@@ -2122,7 +2117,7 @@
     </row>
     <row r="12" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="8">
         <v>19977</v>
@@ -2196,7 +2191,7 @@
     </row>
     <row r="13" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="13">
         <v>23601</v>
@@ -2270,7 +2265,7 @@
     </row>
     <row r="14" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="8">
         <v>459675</v>
@@ -2344,7 +2339,7 @@
     </row>
     <row r="15" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="13">
         <v>189481</v>
@@ -2418,7 +2413,7 @@
     </row>
     <row r="16" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="8">
         <v>36536</v>
@@ -2492,7 +2487,7 @@
     </row>
     <row r="17" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="13">
         <v>29261</v>
@@ -2566,7 +2561,7 @@
     </row>
     <row r="18" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="8">
         <v>261977</v>
@@ -2640,7 +2635,7 @@
     </row>
     <row r="19" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="13">
         <v>98474</v>
@@ -2714,7 +2709,7 @@
     </row>
     <row r="20" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="8">
         <v>62059</v>
@@ -2788,7 +2783,7 @@
     </row>
     <row r="21" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="13">
         <v>67470</v>
@@ -2862,7 +2857,7 @@
     </row>
     <row r="22" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="8">
         <v>97834</v>
@@ -2936,7 +2931,7 @@
     </row>
     <row r="23" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="13">
         <v>92844</v>
@@ -3010,7 +3005,7 @@
     </row>
     <row r="24" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8">
         <v>25111</v>
@@ -3084,7 +3079,7 @@
     </row>
     <row r="25" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="13">
         <v>132389</v>
@@ -3158,7 +3153,7 @@
     </row>
     <row r="26" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="8">
         <v>117883</v>
@@ -3232,7 +3227,7 @@
     </row>
     <row r="27" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="13">
         <v>280305</v>
@@ -3306,7 +3301,7 @@
     </row>
     <row r="28" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="8">
         <v>104242</v>
@@ -3380,7 +3375,7 @@
     </row>
     <row r="29" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="13">
         <v>77461</v>
@@ -3454,7 +3449,7 @@
     </row>
     <row r="30" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" s="8">
         <v>104430</v>
@@ -3528,7 +3523,7 @@
     </row>
     <row r="31" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="13">
         <v>24678</v>
@@ -3602,7 +3597,7 @@
     </row>
     <row r="32" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="8">
         <v>31194</v>
@@ -3676,7 +3671,7 @@
     </row>
     <row r="33" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" s="13">
         <v>81281</v>
@@ -3750,7 +3745,7 @@
     </row>
     <row r="34" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" s="8">
         <v>23679</v>
@@ -3824,7 +3819,7 @@
     </row>
     <row r="35" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="13">
         <v>158481</v>
@@ -3898,7 +3893,7 @@
     </row>
     <row r="36" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="8">
         <v>36597</v>
@@ -3972,7 +3967,7 @@
     </row>
     <row r="37" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="13">
         <v>299420</v>
@@ -4046,7 +4041,7 @@
     </row>
     <row r="38" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" s="8">
         <v>207837</v>
@@ -4120,7 +4115,7 @@
     </row>
     <row r="39" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" s="13">
         <v>9892</v>
@@ -4194,7 +4189,7 @@
     </row>
     <row r="40" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="8">
         <v>261396</v>
@@ -4268,7 +4263,7 @@
     </row>
     <row r="41" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="13">
         <v>77356</v>
@@ -4342,7 +4337,7 @@
     </row>
     <row r="42" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="8">
         <v>126621</v>
@@ -4416,7 +4411,7 @@
     </row>
     <row r="43" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="13">
         <v>262158</v>
@@ -4490,7 +4485,7 @@
     </row>
     <row r="44" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="8">
         <v>26845</v>
@@ -4564,7 +4559,7 @@
     </row>
     <row r="45" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" s="13">
         <v>61634</v>
@@ -4638,7 +4633,7 @@
     </row>
     <row r="46" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" s="8">
         <v>15408</v>
@@ -4712,7 +4707,7 @@
     </row>
     <row r="47" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" s="13">
         <v>122080</v>
@@ -4786,7 +4781,7 @@
     </row>
     <row r="48" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="8">
         <v>597821</v>
@@ -4860,7 +4855,7 @@
     </row>
     <row r="49" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" s="13">
         <v>97935</v>
@@ -4934,7 +4929,7 @@
     </row>
     <row r="50" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" s="8">
         <v>9389</v>
@@ -5008,7 +5003,7 @@
     </row>
     <row r="51" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" s="13">
         <v>165458</v>
@@ -5082,7 +5077,7 @@
     </row>
     <row r="52" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="8">
         <v>261801</v>
@@ -5156,7 +5151,7 @@
     </row>
     <row r="53" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="13">
         <v>39539</v>
@@ -5192,7 +5187,7 @@
         <v>91.122699999999995</v>
       </c>
       <c r="M53" s="39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N53" s="15">
         <v>7.6E-3</v>
@@ -5230,7 +5225,7 @@
     </row>
     <row r="54" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54" s="8">
         <v>136478</v>
@@ -5304,7 +5299,7 @@
     </row>
     <row r="55" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B55" s="19">
         <v>13454</v>
